--- a/output/tables/GD/finished tables/FIS_CI.xlsx
+++ b/output/tables/GD/finished tables/FIS_CI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\GD\finished tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC0A0B3-0ECB-4E50-85E5-5AD937C8C811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE2FCDC-920F-46ED-966E-B92745D7B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{50C12F1E-A6B5-4E81-A672-15779943F345}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -633,12 +633,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -649,6 +643,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1051,426 +1057,426 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="10">
         <v>-7.7000000000000002E-3</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="10">
         <v>3.15E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="12">
         <v>-7.2300000000000003E-2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="12">
         <v>7.9600000000000004E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="10">
         <v>-4.2299999999999997E-2</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="10">
         <v>0.1628</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="12">
         <v>-7.1800000000000003E-2</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="12">
         <v>6.4600000000000005E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="10">
         <v>-5.2699999999999997E-2</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="10">
         <v>5.9799999999999999E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="12">
         <v>-4.7199999999999999E-2</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="12">
         <v>2.98E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="10">
         <v>-5.1900000000000002E-2</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="10">
         <v>4.1700000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>-3.8E-3</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="12">
         <v>3.6299999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="10">
         <v>-6.2100000000000002E-2</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="10">
         <v>3.3599999999999998E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="12">
         <v>-2.98E-2</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="12">
         <v>3.7600000000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="10">
         <v>-1.2E-2</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="10">
         <v>2.1399999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="12">
         <v>-2.9100000000000001E-2</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="12">
         <v>9.35E-2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="7"/>
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="10">
         <v>-4.9500000000000002E-2</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="10">
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="12">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="12">
         <v>7.6300000000000007E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="10">
         <v>-1.4500000000000001E-2</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="10">
         <v>4.0599999999999997E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="7" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>-1.7299999999999999E-2</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>4.9700000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="10">
         <v>-3.3700000000000001E-2</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="10">
         <v>4.3200000000000002E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="5" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="12">
         <v>-3.1699999999999999E-2</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="12">
         <v>0.13170000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="4" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="10">
         <v>-0.1263</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="10">
         <v>2.6599999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="12">
         <v>-0.15140000000000001</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="12">
         <v>9.8299999999999998E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="10">
         <v>-5.3999999999999999E-2</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="10">
         <v>5.2200000000000003E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="12">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="12">
         <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="10">
         <v>-3.4000000000000002E-2</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="10">
         <v>6.7299999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="7"/>
+      <c r="B25" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="12">
         <v>-9.4999999999999998E-3</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="12">
         <v>5.5800000000000002E-2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="4" t="s">
+      <c r="A26" s="7"/>
+      <c r="B26" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="10">
         <v>-5.9799999999999999E-2</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="10">
         <v>3.8899999999999997E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="7"/>
+      <c r="B27" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="12">
         <v>-4.5999999999999999E-2</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="12">
         <v>2.1700000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="4" t="s">
+      <c r="A28" s="7"/>
+      <c r="B28" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="10">
         <v>1.03E-2</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="10">
         <v>6.3E-2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="5" t="s">
+      <c r="A29" s="7"/>
+      <c r="B29" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="12">
         <v>-3.78E-2</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="12">
         <v>4.7199999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="4" t="s">
+      <c r="A30" s="7"/>
+      <c r="B30" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="10">
         <v>-4.1500000000000002E-2</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="10">
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="5" t="s">
+      <c r="A31" s="7"/>
+      <c r="B31" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="12">
         <v>-5.8099999999999999E-2</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="12">
         <v>3.95E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="4" t="s">
+      <c r="A32" s="7"/>
+      <c r="B32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="10">
         <v>-2.69E-2</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="10">
         <v>0.03</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="7"/>
+      <c r="B33" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="12">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="12">
         <v>5.5800000000000002E-2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="4" t="s">
+      <c r="A34" s="7"/>
+      <c r="B34" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="10">
         <v>-0.08</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="10">
         <v>-4.1000000000000003E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="5" t="s">
+      <c r="A35" s="7"/>
+      <c r="B35" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="12">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="12">
         <v>5.5800000000000002E-2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="4" t="s">
+      <c r="A36" s="8"/>
+      <c r="B36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="2">
         <v>-3.8199999999999998E-2</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="2">
         <v>2.23E-2</v>
       </c>
     </row>
